--- a/modelado/modelos/resultados/Regre/DL_reg.xlsx
+++ b/modelado/modelos/resultados/Regre/DL_reg.xlsx
@@ -10,6 +10,7 @@
     <sheet name="StackedCNN3D_HKP" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="UNet3D_HKP" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="StackedCNN3D_SQA" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="UNet3D_SQA" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
@@ -147,7 +148,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9429750" cy="2847975"/>
+    <ext cx="9344025" cy="2847975"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -208,7 +209,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9486900" cy="2847975"/>
+    <ext cx="9344025" cy="2847975"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -283,6 +284,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -294,7 +298,65 @@
       <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7934325" cy="2990850"/>
+    <ext cx="8172450" cy="2990850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9391650" cy="2847975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8172450" cy="2990850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -595,7 +657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M15"/>
+  <dimension ref="A2:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -668,67 +730,67 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.554±0.007</t>
+          <t>0.571±0.010</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.746±0.005</t>
+          <t>0.756±0.006</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.813±0.039</t>
+          <t>0.861±0.022</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.540±0.011</t>
+          <t>0.546±0.009</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.740±0.014</t>
+          <t>1.706±0.019</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.175±0.001</t>
+          <t>0.171±0.002</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.156±0.032</t>
+          <t>1.122±0.021</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.019±0.091</t>
+          <t>-0.057±0.054</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.689±0.047</t>
+          <t>0.679±0.037</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.709±0.005</t>
+          <t>0.717±0.005</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>55.867±0.595</t>
+          <t>56.244±1.051</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>54.756±1.093</t>
+          <t>54.867±0.626</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>38.938±0.769</t>
+          <t>38.060±1.171</t>
         </is>
       </c>
     </row>
@@ -767,22 +829,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.5506 ± 0.1623</t>
+          <t>0.7071 ± 0.1229</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.1145 ± 0.0283</t>
+          <t>0.1565 ± 0.0223</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.7265 ± 0.4441</t>
+          <t>2.2006 ± 0.2991</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>100.2564 ± 29.7902</t>
+          <t>124.9554 ± 21.9998</t>
         </is>
       </c>
     </row>
@@ -794,238 +856,157 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.3003 ± 0.1927</t>
+          <t>0.3445 ± 0.1191</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0516 ± 0.0179</t>
+          <t>0.0688 ± 0.0305</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.9389 ± 0.5162</t>
+          <t>1.0993 ± 0.2953</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>54.7423 ± 35.3597</t>
+          <t>60.7509 ± 20.4204</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>zo</t>
+          <t>to</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.1593 ± 0.0431</t>
+          <t>0.1417 ± 0.0802</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0298 ± 0.0290</t>
+          <t>0.0374 ± 0.0277</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.5512 ± 0.1197</t>
+          <t>0.5264 ± 0.2802</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>28.9765 ± 7.7910</t>
+          <t>24.9838 ± 14.1703</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>mlotst</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0987 ± 0.0388</t>
+          <t>0.1165 ± 0.0334</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0256 ± 0.0218</t>
+          <t>0.0232 ± 0.0181</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.3789 ± 0.1400</t>
+          <t>0.3924 ± 0.1137</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17.9458 ± 7.0560</t>
+          <t>20.5647 ± 5.8856</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>month_sin</t>
+          <t>month_cos</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.0885 ± 0.0702</t>
+          <t>0.0681 ± 0.0355</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0197 ± 0.0112</t>
+          <t>0.0310 ± 0.0271</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.2801 ± 0.2026</t>
+          <t>0.2618 ± 0.1159</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>16.1080 ± 12.8320</t>
+          <t>12.0272 ± 6.2912</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mlotst</t>
+          <t>month_sin</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.0882 ± 0.0253</t>
+          <t>0.0634 ± 0.0443</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0060 ± 0.0186</t>
+          <t>0.0147 ± 0.0168</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.2819 ± 0.0588</t>
+          <t>0.2418 ± 0.1635</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16.0849 ± 4.7514</t>
+          <t>11.1979 ± 7.7977</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>to_b</t>
+          <t>CDM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.0789 ± 0.0183</t>
+          <t>0.0030 ± 0.0080</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0438 ± 0.0397</t>
+          <t>-0.0006 ± 0.0080</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.2700 ± 0.0622</t>
+          <t>0.0093 ± 0.0288</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14.3418 ± 3.2688</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>month_cos</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0.0690 ± 0.0393</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0.0102 ± 0.0265</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>0.2281 ± 0.1158</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>12.5980 ± 7.2265</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>so</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>0.0167 ± 0.0173</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0.0041 ± 0.0021</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0.0519 ± 0.0564</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>3.0596 ± 3.1455</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CDM</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>0.0109 ± 0.0066</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>-0.0059 ± 0.0172</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.0301 ± 0.0264</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1.9972 ± 1.2146</t>
+          <t>0.5217 ± 1.4207</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M15"/>
+  <dimension ref="A2:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -1114,67 +1095,67 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.578±0.004</t>
+          <t>0.577±0.009</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.761±0.003</t>
+          <t>0.762±0.006</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.852±0.021</t>
+          <t>0.846±0.036</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.553±0.007</t>
+          <t>0.552±0.008</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.692±0.009</t>
+          <t>1.693±0.018</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.170±0.001</t>
+          <t>0.170±0.002</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.130±0.033</t>
+          <t>1.120±0.032</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.077±0.035</t>
+          <t>-0.110±0.066</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.733±0.056</t>
+          <t>0.714±0.059</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.721±0.002</t>
+          <t>0.721±0.005</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>56.578±0.848</t>
+          <t>56.722±1.020</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>55.533±0.467</t>
+          <t>55.567±0.949</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>38.409±0.551</t>
+          <t>38.554±1.004</t>
         </is>
       </c>
     </row>
@@ -1213,265 +1194,184 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.1603 ± 0.1203</t>
+          <t>0.2586 ± 0.1685</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0725 ± 0.0673</t>
+          <t>0.1052 ± 0.0474</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.5863 ± 0.3978</t>
+          <t>0.8953 ± 0.4895</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28.0036 ± 21.2571</t>
+          <t>44.9282 ± 28.7681</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ugo</t>
+          <t>month_sin</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.1045 ± 0.0541</t>
+          <t>0.0908 ± 0.0607</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0472 ± 0.0173</t>
+          <t>0.0229 ± 0.0262</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.3635 ± 0.1931</t>
+          <t>0.2619 ± 0.1712</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18.1423 ± 9.3093</t>
+          <t>15.8797 ± 10.7350</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mlotst</t>
+          <t>ugo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.0632 ± 0.0369</t>
+          <t>0.0763 ± 0.0587</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0255 ± 0.0406</t>
+          <t>0.0486 ± 0.0280</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.2036 ± 0.1066</t>
+          <t>0.2820 ± 0.2041</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10.9988 ± 6.4031</t>
+          <t>13.2842 ± 10.1851</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>month_cos</t>
+          <t>mlotst</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0427 ± 0.0198</t>
+          <t>0.0458 ± 0.0240</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0323 ± 0.0150</t>
+          <t>0.0094 ± 0.0303</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.1442 ± 0.0624</t>
+          <t>0.1507 ± 0.0777</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7.4401 ± 3.4554</t>
+          <t>7.9512 ± 4.1130</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>month_sin</t>
+          <t>month_cos</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.0308 ± 0.0103</t>
+          <t>0.0239 ± 0.0189</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0244 ± 0.0481</t>
+          <t>0.0103 ± 0.0133</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.1012 ± 0.0339</t>
+          <t>0.0901 ± 0.0714</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5.3554 ± 1.7722</t>
+          <t>4.1795 ± 3.3050</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>to_b</t>
+          <t>to</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.0249 ± 0.0175</t>
+          <t>0.0229 ± 0.0186</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0461 ± 0.0300</t>
+          <t>0.0103 ± 0.0301</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.0964 ± 0.0603</t>
+          <t>0.0833 ± 0.0725</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4.3255 ± 3.0306</t>
+          <t>4.0193 ± 3.3115</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>CDM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.0184 ± 0.0074</t>
+          <t>0.0174 ± 0.0145</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0083 ± 0.0278</t>
+          <t>-0.0026 ± 0.0119</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.0707 ± 0.0297</t>
+          <t>0.0528 ± 0.0457</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3.2059 ± 1.2690</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CDM</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0.0142 ± 0.0135</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>-0.0019 ± 0.0181</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>0.0455 ± 0.0535</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2.4714 ± 2.3427</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>so</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>0.0024 ± 0.0028</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0.0127 ± 0.0262</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0.0127 ± 0.0129</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0.4166 ± 0.4887</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>zo</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>0.0004 ± 0.0058</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0.0035 ± 0.0221</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.0019 ± 0.0166</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0.0684 ± 1.0132</t>
+          <t>3.0026 ± 2.4805</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M15"/>
+  <dimension ref="A2:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -1560,67 +1460,67 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.416±0.021</t>
+          <t>0.436±0.015</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.652±0.015</t>
+          <t>0.663±0.012</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.733±0.024</t>
+          <t>0.746±0.026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.279±0.025</t>
+          <t>0.270±0.044</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.286±0.023</t>
+          <t>1.265±0.017</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.099±0.002</t>
+          <t>0.097±0.001</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.702±0.019</t>
+          <t>0.694±0.026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.005±0.068</t>
+          <t>-0.003±0.039</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.376±0.048</t>
+          <t>0.379±0.031</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.572±0.030</t>
+          <t>0.552±0.037</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>66.244±1.416</t>
+          <t>66.444±1.336</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>66.744±1.198</t>
+          <t>66.922±1.207</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>30.575±2.325</t>
+          <t>31.274±1.887</t>
         </is>
       </c>
     </row>
@@ -1659,22 +1559,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.2622 ± 0.1028</t>
+          <t>0.2995 ± 0.0788</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0061 ± 0.0186</t>
+          <t>0.0064 ± 0.0344</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.3960 ± 0.1348</t>
+          <t>0.4730 ± 0.0983</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>63.1677 ± 24.1105</t>
+          <t>68.9995 ± 17.4257</t>
         </is>
       </c>
     </row>
@@ -1686,238 +1586,522 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.1489 ± 0.0983</t>
+          <t>0.1881 ± 0.1320</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0966 ± 0.0589</t>
+          <t>0.1152 ± 0.0783</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.2506 ± 0.1616</t>
+          <t>0.2930 ± 0.1822</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>36.1758 ± 24.5270</t>
+          <t>42.7085 ± 28.8379</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ugo</t>
+          <t>mlotst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.1044 ± 0.0628</t>
+          <t>0.1408 ± 0.1136</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0223 ± 0.0232</t>
+          <t>0.0175 ± 0.0246</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.2084 ± 0.1014</t>
+          <t>0.2307 ± 0.1663</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>24.9164 ± 14.3228</t>
+          <t>32.0453 ± 24.9931</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mlotst</t>
+          <t>ugo</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0900 ± 0.0570</t>
+          <t>0.0976 ± 0.0614</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0078 ± 0.0368</t>
+          <t>-0.0022 ± 0.0473</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.1610 ± 0.0886</t>
+          <t>0.1899 ± 0.0989</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>21.6520 ± 13.2215</t>
+          <t>22.5024 ± 14.1192</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>month_sin</t>
+          <t>to</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.0637 ± 0.0435</t>
+          <t>0.0595 ± 0.0408</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0387 ± 0.0232</t>
+          <t>-0.0059 ± 0.0274</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.0976 ± 0.0809</t>
+          <t>0.0964 ± 0.0624</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>15.5136 ± 10.8010</t>
+          <t>13.5596 ± 8.9704</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>month_sin</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.0593 ± 0.0546</t>
+          <t>0.0582 ± 0.0341</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0068 ± 0.0224</t>
+          <t>0.0493 ± 0.0356</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.0919 ± 0.0926</t>
+          <t>0.0934 ± 0.0486</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>14.4771 ± 13.3730</t>
+          <t>13.5902 ± 8.1610</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>to_b</t>
+          <t>CDM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.0330 ± 0.0270</t>
+          <t>0.0093 ± 0.0169</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0292 ± 0.0379</t>
+          <t>0.0160 ± 0.0275</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.0472 ± 0.0350</t>
+          <t>0.0250 ± 0.0250</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8.0970 ± 6.9188</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>zo</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0.0310 ± 0.0241</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0.0175 ± 0.0345</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>0.0631 ± 0.0483</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>7.6451 ± 6.2370</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>so</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>0.0288 ± 0.0326</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0.0426 ± 0.0209</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0.0558 ± 0.0525</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>6.7988 ± 7.4467</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+          <t>2.1674 ± 3.9302</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:M12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>pearson_corr</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>r2_plot</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>mean_ssim</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>rmse</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>nrmse</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>mae</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>mbe</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>w_dist</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>spearman_corr</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>hit_rate_percent</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>mean_yearly_hit_rate</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>mean_monthly_hit_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0.438±0.016</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.665±0.012</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.757±0.034</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.240±0.048</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.262±0.018</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.097±0.001</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.695±0.035</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-0.033±0.043</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.402±0.037</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.578±0.039</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>67.200±1.744</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>67.622±1.594</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>32.128±1.820</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>variable</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>r2_importance</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>ssim_importance</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>loss_importance</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>r2_drop_%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>vgo</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.1814 ± 0.0705</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.0523 ± 0.0487</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.3165 ± 0.0976</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>41.7642 ± 16.2922</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>month_cos</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.1166 ± 0.1351</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.0712 ± 0.0605</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.1724 ± 0.1949</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>27.2151 ± 31.5731</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>mlotst</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.0975 ± 0.0582</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.0124 ± 0.0321</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.1712 ± 0.0996</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>22.3087 ± 12.5718</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.0327 ± 0.0488</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.0077 ± 0.0183</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.0522 ± 0.0742</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7.3684 ± 10.6363</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>month_sin</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.0319 ± 0.0370</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.0160 ± 0.0177</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.0495 ± 0.0451</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>7.2459 ± 8.1174</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ugo</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.0141 ± 0.0141</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.0138 ± 0.0284</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.0311 ± 0.0188</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3.2471 ± 3.3061</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>CDM</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>0.0102 ± 0.0159</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>-0.0037 ± 0.0176</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.0170 ± 0.0232</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2.4248 ± 3.7555</t>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.0063 ± 0.0176</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-0.0039 ± 0.0211</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.0101 ± 0.0290</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.4392 ± 4.0571</t>
         </is>
       </c>
     </row>

--- a/modelado/modelos/resultados/Regre/DL_reg.xlsx
+++ b/modelado/modelos/resultados/Regre/DL_reg.xlsx
@@ -223,9 +223,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -251,9 +248,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -345,6 +339,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -370,6 +367,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1095,67 +1095,67 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.577±0.009</t>
+          <t>0.574±0.008</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.762±0.006</t>
+          <t>0.759±0.005</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.846±0.036</t>
+          <t>0.842±0.013</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.552±0.008</t>
+          <t>0.548±0.007</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.693±0.018</t>
+          <t>1.700±0.015</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.170±0.002</t>
+          <t>0.171±0.002</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.120±0.032</t>
+          <t>1.121±0.023</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.110±0.066</t>
+          <t>-0.095±0.054</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.714±0.059</t>
+          <t>0.710±0.030</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.721±0.005</t>
+          <t>0.719±0.004</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>56.722±1.020</t>
+          <t>57.093±1.156</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>55.567±0.949</t>
+          <t>55.722±0.782</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>38.554±1.004</t>
+          <t>38.983±0.803</t>
         </is>
       </c>
     </row>
@@ -1189,54 +1189,54 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>vgo</t>
+          <t>mlotst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.2586 ± 0.1685</t>
+          <t>0.0825 ± 0.0466</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.1052 ± 0.0474</t>
+          <t>0.0586 ± 0.0314</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.8953 ± 0.4895</t>
+          <t>0.2676 ± 0.1454</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>44.9282 ± 28.7681</t>
+          <t>14.5499 ± 8.3421</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>month_sin</t>
+          <t>vgo</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.0908 ± 0.0607</t>
+          <t>0.0806 ± 0.0545</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0229 ± 0.0262</t>
+          <t>0.0516 ± 0.0541</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.2619 ± 0.1712</t>
+          <t>0.3448 ± 0.2223</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15.8797 ± 10.7350</t>
+          <t>14.0690 ± 9.4182</t>
         </is>
       </c>
     </row>
@@ -1248,130 +1248,130 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.0763 ± 0.0587</t>
+          <t>0.0620 ± 0.0247</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0486 ± 0.0280</t>
+          <t>0.0532 ± 0.0142</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.2820 ± 0.2041</t>
+          <t>0.2474 ± 0.0942</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13.2842 ± 10.1851</t>
+          <t>10.9005 ± 4.3961</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mlotst</t>
+          <t>month_sin</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0458 ± 0.0240</t>
+          <t>0.0540 ± 0.0542</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0094 ± 0.0303</t>
+          <t>0.0051 ± 0.0187</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.1507 ± 0.0777</t>
+          <t>0.1618 ± 0.1737</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7.9512 ± 4.1130</t>
+          <t>9.4065 ± 9.4466</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>month_cos</t>
+          <t>to</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.0239 ± 0.0189</t>
+          <t>0.0183 ± 0.0122</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0103 ± 0.0133</t>
+          <t>0.0138 ± 0.0212</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.0901 ± 0.0714</t>
+          <t>0.0720 ± 0.0479</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4.1795 ± 3.3050</t>
+          <t>3.2008 ± 2.1250</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>CDM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.0229 ± 0.0186</t>
+          <t>0.0119 ± 0.0079</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0103 ± 0.0301</t>
+          <t>0.0079 ± 0.0149</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.0833 ± 0.0725</t>
+          <t>0.0331 ± 0.0262</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4.0193 ± 3.3115</t>
+          <t>2.0812 ± 1.3632</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CDM</t>
+          <t>month_cos</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.0174 ± 0.0145</t>
+          <t>0.0096 ± 0.0102</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.0026 ± 0.0119</t>
+          <t>0.0181 ± 0.0161</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.0528 ± 0.0457</t>
+          <t>0.0383 ± 0.0387</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3.0026 ± 2.4805</t>
+          <t>1.6727 ± 1.7650</t>
         </is>
       </c>
     </row>

--- a/modelado/modelos/resultados/Regre/DL_reg.xlsx
+++ b/modelado/modelos/resultados/Regre/DL_reg.xlsx
@@ -1095,67 +1095,67 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.574±0.008</t>
+          <t>0.575±0.006</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.759±0.005</t>
+          <t>0.759±0.003</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.842±0.013</t>
+          <t>0.841±0.020</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.548±0.007</t>
+          <t>0.548±0.008</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.700±0.015</t>
+          <t>1.698±0.012</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.171±0.002</t>
+          <t>0.171±0.001</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.121±0.023</t>
+          <t>1.122±0.026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.095±0.054</t>
+          <t>-0.093±0.061</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.710±0.030</t>
+          <t>0.710±0.050</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.719±0.004</t>
+          <t>0.721±0.004</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>57.093±1.156</t>
+          <t>56.811±0.872</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>55.722±0.782</t>
+          <t>55.667±0.537</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>38.983±0.803</t>
+          <t>38.549±0.647</t>
         </is>
       </c>
     </row>
@@ -1189,81 +1189,81 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mlotst</t>
+          <t>vgo</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.0825 ± 0.0466</t>
+          <t>0.0852 ± 0.0559</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0586 ± 0.0314</t>
+          <t>0.0277 ± 0.0295</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.2676 ± 0.1454</t>
+          <t>0.3531 ± 0.2075</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14.5499 ± 8.3421</t>
+          <t>14.9029 ± 9.8108</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>vgo</t>
+          <t>ugo</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.0806 ± 0.0545</t>
+          <t>0.0839 ± 0.0403</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0516 ± 0.0541</t>
+          <t>0.0301 ± 0.0185</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.3448 ± 0.2223</t>
+          <t>0.3167 ± 0.1478</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.0690 ± 9.4182</t>
+          <t>14.6429 ± 6.9987</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ugo</t>
+          <t>mlotst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.0620 ± 0.0247</t>
+          <t>0.0827 ± 0.0409</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0532 ± 0.0142</t>
+          <t>0.0377 ± 0.0355</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.2474 ± 0.0942</t>
+          <t>0.2546 ± 0.1158</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10.9005 ± 4.3961</t>
+          <t>14.4724 ± 7.1320</t>
         </is>
       </c>
     </row>
@@ -1275,22 +1275,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0540 ± 0.0542</t>
+          <t>0.0423 ± 0.0662</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0051 ± 0.0187</t>
+          <t>0.0156 ± 0.0160</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.1618 ± 0.1737</t>
+          <t>0.1207 ± 0.1740</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>9.4065 ± 9.4466</t>
+          <t>7.3951 ± 11.5466</t>
         </is>
       </c>
     </row>
@@ -1302,22 +1302,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.0183 ± 0.0122</t>
+          <t>0.0369 ± 0.0359</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0138 ± 0.0212</t>
+          <t>0.0075 ± 0.0271</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.0720 ± 0.0479</t>
+          <t>0.1438 ± 0.1284</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.2008 ± 2.1250</t>
+          <t>6.4608 ± 6.2904</t>
         </is>
       </c>
     </row>
@@ -1329,22 +1329,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.0119 ± 0.0079</t>
+          <t>0.0129 ± 0.0063</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0079 ± 0.0149</t>
+          <t>0.0061 ± 0.0263</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.0331 ± 0.0262</t>
+          <t>0.0416 ± 0.0243</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.0812 ± 1.3632</t>
+          <t>2.2582 ± 1.0883</t>
         </is>
       </c>
     </row>
@@ -1356,22 +1356,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.0096 ± 0.0102</t>
+          <t>0.0082 ± 0.0122</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0181 ± 0.0161</t>
+          <t>0.0068 ± 0.0140</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.0383 ± 0.0387</t>
+          <t>0.0278 ± 0.0443</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.6727 ± 1.7650</t>
+          <t>1.4209 ± 2.1284</t>
         </is>
       </c>
     </row>

--- a/modelado/modelos/resultados/Regre/DL_reg.xlsx
+++ b/modelado/modelos/resultados/Regre/DL_reg.xlsx
@@ -730,27 +730,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.571±0.010</t>
+          <t>0.570±0.010</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.756±0.006</t>
+          <t>0.757±0.007</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.861±0.022</t>
+          <t>0.865±0.018</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.546±0.009</t>
+          <t>0.514±0.011</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.706±0.019</t>
+          <t>1.707±0.020</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -760,37 +760,37 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.122±0.021</t>
+          <t>1.150±0.040</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.057±0.054</t>
+          <t>-0.061±0.067</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.679±0.037</t>
+          <t>0.734±0.072</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.717±0.005</t>
+          <t>0.719±0.006</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>56.244±1.051</t>
+          <t>56.333±1.225</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>54.867±0.626</t>
+          <t>54.767±0.939</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>38.060±1.171</t>
+          <t>38.990±1.006</t>
         </is>
       </c>
     </row>
@@ -829,49 +829,49 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.7071 ± 0.1229</t>
+          <t>0.3723 ± 0.0896</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.1565 ± 0.0223</t>
+          <t>0.0847 ± 0.0328</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.2006 ± 0.2991</t>
+          <t>1.3305 ± 0.2991</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>124.9554 ± 21.9998</t>
+          <t>65.6542 ± 15.5530</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ugo</t>
+          <t>mlotst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.3445 ± 0.1191</t>
+          <t>0.1094 ± 0.0369</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0688 ± 0.0305</t>
+          <t>0.0185 ± 0.0180</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.0993 ± 0.2953</t>
+          <t>0.3582 ± 0.1185</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>60.7509 ± 20.4204</t>
+          <t>19.3396 ± 6.6318</t>
         </is>
       </c>
     </row>
@@ -883,103 +883,103 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.1417 ± 0.0802</t>
+          <t>0.0949 ± 0.0641</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0374 ± 0.0277</t>
+          <t>0.0272 ± 0.0151</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.5264 ± 0.2802</t>
+          <t>0.3639 ± 0.2396</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>24.9838 ± 14.1703</t>
+          <t>16.6850 ± 11.1508</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mlotst</t>
+          <t>ugo</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.1165 ± 0.0334</t>
+          <t>0.0840 ± 0.0118</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0232 ± 0.0181</t>
+          <t>0.0058 ± 0.0420</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.3924 ± 0.1137</t>
+          <t>0.3213 ± 0.0431</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20.5647 ± 5.8856</t>
+          <t>14.8205 ± 2.0330</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>month_cos</t>
+          <t>month_sin</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.0681 ± 0.0355</t>
+          <t>0.0416 ± 0.0322</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0310 ± 0.0271</t>
+          <t>0.0152 ± 0.0147</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.2618 ± 0.1159</t>
+          <t>0.1465 ± 0.1067</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12.0272 ± 6.2912</t>
+          <t>7.3170 ± 5.5841</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>month_sin</t>
+          <t>month_cos</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.0634 ± 0.0443</t>
+          <t>0.0347 ± 0.0500</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0147 ± 0.0168</t>
+          <t>0.0102 ± 0.0281</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.2418 ± 0.1635</t>
+          <t>0.1383 ± 0.1934</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11.1979 ± 7.7977</t>
+          <t>6.1561 ± 8.9416</t>
         </is>
       </c>
     </row>
@@ -991,22 +991,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.0030 ± 0.0080</t>
+          <t>0.0163 ± 0.0072</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.0006 ± 0.0080</t>
+          <t>-0.0021 ± 0.0091</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.0093 ± 0.0288</t>
+          <t>0.0544 ± 0.0252</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.5217 ± 1.4207</t>
+          <t>2.8677 ± 1.2629</t>
         </is>
       </c>
     </row>
@@ -1095,67 +1095,67 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.575±0.006</t>
+          <t>0.577±0.006</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.759±0.003</t>
+          <t>0.764±0.003</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.841±0.020</t>
+          <t>0.816±0.023</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.548±0.008</t>
+          <t>0.507±0.029</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.698±0.012</t>
+          <t>1.697±0.013</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.171±0.001</t>
+          <t>0.145±0.001</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.122±0.026</t>
+          <t>1.162±0.021</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.093±0.061</t>
+          <t>-0.146±0.078</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.710±0.050</t>
+          <t>0.798±0.045</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.721±0.004</t>
+          <t>0.725±0.004</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>56.811±0.872</t>
+          <t>55.389±1.135</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>55.667±0.537</t>
+          <t>54.411±1.091</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>38.549±0.647</t>
+          <t>39.237±0.952</t>
         </is>
       </c>
     </row>
@@ -1189,54 +1189,54 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>vgo</t>
+          <t>ugo</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.0852 ± 0.0559</t>
+          <t>0.0701 ± 0.0386</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0277 ± 0.0295</t>
+          <t>0.0048 ± 0.0204</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.3531 ± 0.2075</t>
+          <t>0.2727 ± 0.1486</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14.9029 ± 9.8108</t>
+          <t>12.1892 ± 6.6992</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ugo</t>
+          <t>vgo</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.0839 ± 0.0403</t>
+          <t>0.0603 ± 0.0352</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0301 ± 0.0185</t>
+          <t>-0.0005 ± 0.0207</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.3167 ± 0.1478</t>
+          <t>0.2472 ± 0.1391</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.6429 ± 6.9987</t>
+          <t>10.5073 ± 6.1945</t>
         </is>
       </c>
     </row>
@@ -1248,130 +1248,130 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.0827 ± 0.0409</t>
+          <t>0.0587 ± 0.0388</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0377 ± 0.0355</t>
+          <t>0.0214 ± 0.0117</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.2546 ± 0.1158</t>
+          <t>0.2037 ± 0.1419</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14.4724 ± 7.1320</t>
+          <t>10.2089 ± 6.7686</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>month_sin</t>
+          <t>to</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0423 ± 0.0662</t>
+          <t>0.0391 ± 0.0123</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0156 ± 0.0160</t>
+          <t>0.0080 ± 0.0121</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.1207 ± 0.1740</t>
+          <t>0.1505 ± 0.0477</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7.3951 ± 11.5466</t>
+          <t>6.7947 ± 2.1207</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>month_sin</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.0369 ± 0.0359</t>
+          <t>0.0177 ± 0.0100</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0075 ± 0.0271</t>
+          <t>0.0054 ± 0.0090</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.1438 ± 0.1284</t>
+          <t>0.0613 ± 0.0400</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6.4608 ± 6.2904</t>
+          <t>3.0774 ± 1.7209</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CDM</t>
+          <t>month_cos</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.0129 ± 0.0063</t>
+          <t>0.0171 ± 0.0148</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0061 ± 0.0263</t>
+          <t>0.0049 ± 0.0074</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.0416 ± 0.0243</t>
+          <t>0.0557 ± 0.0528</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.2582 ± 1.0883</t>
+          <t>2.9645 ± 2.5735</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>month_cos</t>
+          <t>CDM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.0082 ± 0.0122</t>
+          <t>0.0092 ± 0.0057</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0068 ± 0.0140</t>
+          <t>0.0046 ± 0.0101</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.0278 ± 0.0443</t>
+          <t>0.0338 ± 0.0214</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.4209 ± 2.1284</t>
+          <t>1.6026 ± 0.9920</t>
         </is>
       </c>
     </row>
@@ -1825,27 +1825,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.438±0.016</t>
+          <t>0.439±0.014</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.665±0.012</t>
+          <t>0.666±0.011</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.757±0.034</t>
+          <t>0.780±0.024</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.240±0.048</t>
+          <t>0.206±0.033</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.262±0.018</t>
+          <t>1.261±0.016</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1855,37 +1855,37 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.695±0.035</t>
+          <t>0.716±0.025</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.033±0.043</t>
+          <t>-0.024±0.087</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.402±0.037</t>
+          <t>0.399±0.033</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.578±0.039</t>
+          <t>0.593±0.020</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>67.200±1.744</t>
+          <t>66.478±0.741</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>67.622±1.594</t>
+          <t>66.856±0.823</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>32.128±1.820</t>
+          <t>31.661±1.283</t>
         </is>
       </c>
     </row>
@@ -1919,162 +1919,162 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>vgo</t>
+          <t>month_cos</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.1814 ± 0.0705</t>
+          <t>0.0830 ± 0.0947</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0523 ± 0.0487</t>
+          <t>0.0349 ± 0.0390</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.3165 ± 0.0976</t>
+          <t>0.1314 ± 0.1434</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>41.7642 ± 16.2922</t>
+          <t>19.1968 ± 21.8859</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>month_cos</t>
+          <t>mlotst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.1166 ± 0.1351</t>
+          <t>0.0713 ± 0.0628</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0712 ± 0.0605</t>
+          <t>0.0235 ± 0.0273</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.1724 ± 0.1949</t>
+          <t>0.1361 ± 0.1179</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27.2151 ± 31.5731</t>
+          <t>16.4396 ± 14.3324</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mlotst</t>
+          <t>vgo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.0975 ± 0.0582</t>
+          <t>0.0649 ± 0.0405</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0124 ± 0.0321</t>
+          <t>0.0033 ± 0.0169</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.1712 ± 0.0996</t>
+          <t>0.1188 ± 0.0712</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>22.3087 ± 12.5718</t>
+          <t>14.7500 ± 9.0212</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>ugo</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0327 ± 0.0488</t>
+          <t>0.0509 ± 0.0704</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0077 ± 0.0183</t>
+          <t>0.0039 ± 0.0196</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.0522 ± 0.0742</t>
+          <t>0.0876 ± 0.1165</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7.3684 ± 10.6363</t>
+          <t>11.4100 ± 15.1764</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>month_sin</t>
+          <t>to</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.0319 ± 0.0370</t>
+          <t>0.0374 ± 0.0562</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0160 ± 0.0177</t>
+          <t>-0.0033 ± 0.0351</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.0495 ± 0.0451</t>
+          <t>0.0633 ± 0.0887</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7.2459 ± 8.1174</t>
+          <t>8.6108 ± 12.8318</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ugo</t>
+          <t>month_sin</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.0141 ± 0.0141</t>
+          <t>0.0284 ± 0.0253</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0138 ± 0.0284</t>
+          <t>0.0236 ± 0.0388</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.0311 ± 0.0188</t>
+          <t>0.0499 ± 0.0437</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.2471 ± 3.3061</t>
+          <t>6.5057 ± 5.8585</t>
         </is>
       </c>
     </row>
@@ -2086,22 +2086,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.0063 ± 0.0176</t>
+          <t>0.0162 ± 0.0256</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.0039 ± 0.0211</t>
+          <t>0.0104 ± 0.0141</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.0101 ± 0.0290</t>
+          <t>0.0294 ± 0.0426</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.4392 ± 4.0571</t>
+          <t>3.7379 ± 5.9283</t>
         </is>
       </c>
     </row>

--- a/modelado/modelos/resultados/Regre/DL_reg.xlsx
+++ b/modelado/modelos/resultados/Regre/DL_reg.xlsx
@@ -730,67 +730,67 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.570±0.010</t>
+          <t>0.570±0.008</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.757±0.007</t>
+          <t>0.757±0.005</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.865±0.018</t>
+          <t>0.831±0.023</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.514±0.011</t>
+          <t>0.513±0.014</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.707±0.020</t>
+          <t>1.711±0.017</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.171±0.002</t>
+          <t>0.146±0.001</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.150±0.040</t>
+          <t>1.166±0.016</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.061±0.067</t>
+          <t>-0.088±0.071</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.734±0.072</t>
+          <t>0.770±0.041</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.719±0.006</t>
+          <t>0.719±0.003</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>56.333±1.225</t>
+          <t>55.478±1.084</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>54.767±0.939</t>
+          <t>54.589±0.728</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>38.990±1.006</t>
+          <t>38.804±0.939</t>
         </is>
       </c>
     </row>
@@ -829,103 +829,103 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.3723 ± 0.0896</t>
+          <t>0.3054 ± 0.0724</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0847 ± 0.0328</t>
+          <t>0.0655 ± 0.0203</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.3305 ± 0.2991</t>
+          <t>1.2693 ± 0.2696</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>65.6542 ± 15.5530</t>
+          <t>53.7886 ± 12.3747</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mlotst</t>
+          <t>ugo</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.1094 ± 0.0369</t>
+          <t>0.1302 ± 0.0729</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0185 ± 0.0180</t>
+          <t>0.0268 ± 0.0351</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.3582 ± 0.1185</t>
+          <t>0.5453 ± 0.3035</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19.3396 ± 6.6318</t>
+          <t>22.8827 ± 12.6197</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>mlotst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.0949 ± 0.0641</t>
+          <t>0.0640 ± 0.0441</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0272 ± 0.0151</t>
+          <t>0.0126 ± 0.0119</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.3639 ± 0.2396</t>
+          <t>0.2318 ± 0.1550</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16.6850 ± 11.1508</t>
+          <t>11.2954 ± 7.7646</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ugo</t>
+          <t>to</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0840 ± 0.0118</t>
+          <t>0.0629 ± 0.0346</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0058 ± 0.0420</t>
+          <t>0.0165 ± 0.0195</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.3213 ± 0.0431</t>
+          <t>0.2803 ± 0.1551</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>14.8205 ± 2.0330</t>
+          <t>11.0549 ± 6.0236</t>
         </is>
       </c>
     </row>
@@ -937,22 +937,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.0416 ± 0.0322</t>
+          <t>0.0428 ± 0.0271</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0152 ± 0.0147</t>
+          <t>0.0083 ± 0.0130</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.1465 ± 0.1067</t>
+          <t>0.1706 ± 0.1078</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7.3170 ± 5.5841</t>
+          <t>7.5265 ± 4.7585</t>
         </is>
       </c>
     </row>
@@ -964,22 +964,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.0347 ± 0.0500</t>
+          <t>0.0323 ± 0.0500</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0102 ± 0.0281</t>
+          <t>0.0003 ± 0.0068</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.1383 ± 0.1934</t>
+          <t>0.1215 ± 0.1803</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6.1561 ± 8.9416</t>
+          <t>5.7055 ± 8.8021</t>
         </is>
       </c>
     </row>
@@ -991,22 +991,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.0163 ± 0.0072</t>
+          <t>0.0074 ± 0.0058</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.0021 ± 0.0091</t>
+          <t>0.0001 ± 0.0074</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.0544 ± 0.0252</t>
+          <t>0.0286 ± 0.0225</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.8677 ± 1.2629</t>
+          <t>1.3133 ± 1.0266</t>
         </is>
       </c>
     </row>
@@ -1095,67 +1095,67 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.577±0.006</t>
+          <t>0.585±0.023</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.764±0.003</t>
+          <t>0.787±0.009</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.816±0.023</t>
+          <t>0.702±0.075</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.507±0.029</t>
+          <t>0.515±0.027</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.697±0.013</t>
+          <t>1.765±0.048</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.145±0.001</t>
+          <t>0.181±0.005</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.162±0.021</t>
+          <t>1.196±0.025</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.146±0.078</t>
+          <t>-0.434±0.097</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.798±0.045</t>
+          <t>0.929±0.036</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.725±0.004</t>
+          <t>0.739±0.006</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>55.389±1.135</t>
+          <t>48.033±0.867</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>54.411±1.091</t>
+          <t>48.033±0.867</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>39.237±0.952</t>
+          <t>34.417±0.937</t>
         </is>
       </c>
     </row>
@@ -1189,54 +1189,54 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ugo</t>
+          <t>vgo</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.0701 ± 0.0386</t>
+          <t>0.1318 ± 0.0985</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0048 ± 0.0204</t>
+          <t>0.0265 ± 0.0333</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.2727 ± 0.1486</t>
+          <t>0.6220 ± 0.4420</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12.1892 ± 6.6992</t>
+          <t>22.5579 ± 16.6627</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>vgo</t>
+          <t>ugo</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.0603 ± 0.0352</t>
+          <t>0.0809 ± 0.0488</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.0005 ± 0.0207</t>
+          <t>-0.0052 ± 0.0208</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.2472 ± 0.1391</t>
+          <t>0.3841 ± 0.2238</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10.5073 ± 6.1945</t>
+          <t>14.0094 ± 8.6379</t>
         </is>
       </c>
     </row>
@@ -1248,22 +1248,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.0587 ± 0.0388</t>
+          <t>0.0578 ± 0.0341</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0214 ± 0.0117</t>
+          <t>0.0262 ± 0.0249</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.2037 ± 0.1419</t>
+          <t>0.2247 ± 0.1389</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10.2089 ± 6.7686</t>
+          <t>9.8744 ± 5.8270</t>
         </is>
       </c>
     </row>
@@ -1275,76 +1275,76 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0391 ± 0.0123</t>
+          <t>0.0367 ± 0.0465</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0080 ± 0.0121</t>
+          <t>0.0086 ± 0.0148</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.1505 ± 0.0477</t>
+          <t>0.1775 ± 0.2235</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6.7947 ± 2.1207</t>
+          <t>6.4403 ± 8.4677</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>month_sin</t>
+          <t>month_cos</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.0177 ± 0.0100</t>
+          <t>0.0153 ± 0.0251</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0054 ± 0.0090</t>
+          <t>0.0057 ± 0.0162</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.0613 ± 0.0400</t>
+          <t>0.0646 ± 0.1242</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.0774 ± 1.7209</t>
+          <t>2.5326 ± 4.2062</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>month_cos</t>
+          <t>month_sin</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.0171 ± 0.0148</t>
+          <t>0.0090 ± 0.0181</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0049 ± 0.0074</t>
+          <t>0.0030 ± 0.0078</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.0557 ± 0.0528</t>
+          <t>0.0279 ± 0.0780</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.9645 ± 2.5735</t>
+          <t>1.5779 ± 3.0943</t>
         </is>
       </c>
     </row>
@@ -1356,22 +1356,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.0092 ± 0.0057</t>
+          <t>0.0026 ± 0.0125</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0046 ± 0.0101</t>
+          <t>0.0091 ± 0.0174</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.0338 ± 0.0214</t>
+          <t>0.0082 ± 0.0589</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.6026 ± 0.9920</t>
+          <t>0.4034 ± 2.1578</t>
         </is>
       </c>
     </row>
@@ -1460,67 +1460,67 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.436±0.015</t>
+          <t>0.421±0.030</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.663±0.012</t>
+          <t>0.651±0.024</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.746±0.026</t>
+          <t>0.766±0.035</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.270±0.044</t>
+          <t>0.249±0.037</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.265±0.017</t>
+          <t>1.287±0.032</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.097±0.001</t>
+          <t>0.099±0.002</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.694±0.026</t>
+          <t>0.702±0.030</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.003±0.039</t>
+          <t>-0.023±0.064</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.379±0.031</t>
+          <t>0.424±0.051</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.552±0.037</t>
+          <t>0.540±0.050</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>66.444±1.336</t>
+          <t>67.389±1.800</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>66.922±1.207</t>
+          <t>67.711±1.474</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>31.274±1.887</t>
+          <t>29.460±1.690</t>
         </is>
       </c>
     </row>
@@ -1559,76 +1559,76 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.2995 ± 0.0788</t>
+          <t>0.1921 ± 0.0762</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0064 ± 0.0344</t>
+          <t>0.0312 ± 0.0255</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.4730 ± 0.0983</t>
+          <t>0.4208 ± 0.1508</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>68.9995 ± 17.4257</t>
+          <t>45.2020 ± 17.0786</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>month_cos</t>
+          <t>to</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.1881 ± 0.1320</t>
+          <t>0.1805 ± 0.2120</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.1152 ± 0.0783</t>
+          <t>0.0824 ± 0.1172</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.2930 ± 0.1822</t>
+          <t>0.3679 ± 0.3560</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>42.7085 ± 28.8379</t>
+          <t>46.6456 ± 61.4460</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mlotst</t>
+          <t>month_cos</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.1408 ± 0.1136</t>
+          <t>0.1274 ± 0.1163</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0175 ± 0.0246</t>
+          <t>0.0510 ± 0.0396</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.2307 ± 0.1663</t>
+          <t>0.2610 ± 0.2332</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>32.0453 ± 24.9931</t>
+          <t>31.2075 ± 28.3798</t>
         </is>
       </c>
     </row>
@@ -1640,76 +1640,76 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0976 ± 0.0614</t>
+          <t>0.0975 ± 0.0618</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.0022 ± 0.0473</t>
+          <t>0.0274 ± 0.0252</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.1899 ± 0.0989</t>
+          <t>0.2131 ± 0.1271</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>22.5024 ± 14.1192</t>
+          <t>24.1522 ± 17.7990</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>month_sin</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.0595 ± 0.0408</t>
+          <t>0.0688 ± 0.0309</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.0059 ± 0.0274</t>
+          <t>0.0163 ± 0.0210</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.0964 ± 0.0624</t>
+          <t>0.1411 ± 0.0641</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>13.5596 ± 8.9704</t>
+          <t>16.6958 ± 8.0690</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>month_sin</t>
+          <t>mlotst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.0582 ± 0.0341</t>
+          <t>0.0438 ± 0.0511</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0493 ± 0.0356</t>
+          <t>0.0074 ± 0.0176</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.0934 ± 0.0486</t>
+          <t>0.1132 ± 0.1177</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13.5902 ± 8.1610</t>
+          <t>10.0123 ± 11.7731</t>
         </is>
       </c>
     </row>
@@ -1721,22 +1721,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.0093 ± 0.0169</t>
+          <t>0.0046 ± 0.0138</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0160 ± 0.0275</t>
+          <t>0.0208 ± 0.0171</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.0250 ± 0.0250</t>
+          <t>0.0195 ± 0.0279</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.1674 ± 3.9302</t>
+          <t>1.3146 ± 3.7783</t>
         </is>
       </c>
     </row>
@@ -1825,67 +1825,67 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.439±0.014</t>
+          <t>0.435±0.025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.666±0.011</t>
+          <t>0.671±0.018</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.780±0.024</t>
+          <t>0.715±0.050</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.206±0.033</t>
+          <t>0.236±0.039</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.261±0.016</t>
+          <t>1.332±0.029</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.097±0.001</t>
+          <t>0.116±0.003</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.716±0.025</t>
+          <t>0.721±0.030</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.024±0.087</t>
+          <t>-0.109±0.073</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.399±0.033</t>
+          <t>0.492±0.036</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.593±0.020</t>
+          <t>0.594±0.052</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>66.478±0.741</t>
+          <t>69.233±1.846</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>66.856±0.823</t>
+          <t>69.233±1.846</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>31.661±1.283</t>
+          <t>33.340±2.222</t>
         </is>
       </c>
     </row>
@@ -1919,162 +1919,162 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>month_cos</t>
+          <t>vgo</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.0830 ± 0.0947</t>
+          <t>0.1103 ± 0.0342</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0349 ± 0.0390</t>
+          <t>0.0128 ± 0.0194</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.1314 ± 0.1434</t>
+          <t>0.2639 ± 0.0653</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19.1968 ± 21.8859</t>
+          <t>25.3463 ± 7.5066</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mlotst</t>
+          <t>month_sin</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.0713 ± 0.0628</t>
+          <t>0.0687 ± 0.0553</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0235 ± 0.0273</t>
+          <t>0.0088 ± 0.0134</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.1361 ± 0.1179</t>
+          <t>0.1426 ± 0.1160</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16.4396 ± 14.3324</t>
+          <t>15.6653 ± 12.4544</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>vgo</t>
+          <t>to</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.0649 ± 0.0405</t>
+          <t>0.0547 ± 0.0663</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0033 ± 0.0169</t>
+          <t>0.0464 ± 0.0601</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.1188 ± 0.0712</t>
+          <t>0.0920 ± 0.1583</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14.7500 ± 9.0212</t>
+          <t>12.4504 ± 14.7083</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ugo</t>
+          <t>month_cos</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0509 ± 0.0704</t>
+          <t>0.0478 ± 0.0447</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0039 ± 0.0196</t>
+          <t>0.0100 ± 0.0220</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.0876 ± 0.1165</t>
+          <t>0.0848 ± 0.0821</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11.4100 ± 15.1764</t>
+          <t>11.1414 ± 10.2741</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>ugo</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.0374 ± 0.0562</t>
+          <t>0.0367 ± 0.0396</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.0033 ± 0.0351</t>
+          <t>0.0020 ± 0.0121</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.0633 ± 0.0887</t>
+          <t>0.0885 ± 0.0854</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8.6108 ± 12.8318</t>
+          <t>8.6130 ± 9.3178</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>month_sin</t>
+          <t>mlotst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.0284 ± 0.0253</t>
+          <t>-0.0227 ± 0.0485</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0236 ± 0.0388</t>
+          <t>0.0211 ± 0.0263</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.0499 ± 0.0437</t>
+          <t>-0.0028 ± 0.1238</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6.5057 ± 5.8585</t>
+          <t>-5.4246 ± 11.2706</t>
         </is>
       </c>
     </row>
@@ -2086,22 +2086,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.0162 ± 0.0256</t>
+          <t>-0.0271 ± 0.0229</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0104 ± 0.0141</t>
+          <t>0.0111 ± 0.0235</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.0294 ± 0.0426</t>
+          <t>-0.0533 ± 0.0464</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3.7379 ± 5.9283</t>
+          <t>-6.2919 ± 5.3649</t>
         </is>
       </c>
     </row>

--- a/modelado/modelos/resultados/Regre/DL_reg.xlsx
+++ b/modelado/modelos/resultados/Regre/DL_reg.xlsx
@@ -11,6 +11,7 @@
     <sheet name="UNet3D_HKP" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="StackedCNN3D_SQA" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="UNet3D_SQA" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="CNN3D_SQA" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
@@ -148,7 +149,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9344025" cy="2847975"/>
+    <ext cx="9420225" cy="2847975"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -223,6 +224,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -248,6 +252,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -325,7 +332,62 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9391650" cy="2847975"/>
+    <ext cx="9420225" cy="2847975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8172450" cy="2990850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9420225" cy="2847975"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -730,67 +792,67 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.570±0.008</t>
+          <t>0.584±0.017</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.757±0.005</t>
+          <t>0.778±0.011</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.831±0.023</t>
+          <t>0.714±0.040</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.513±0.014</t>
+          <t>0.517±0.023</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.711±0.017</t>
+          <t>1.768±0.037</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.146±0.001</t>
+          <t>0.181±0.004</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.166±0.016</t>
+          <t>1.226±0.026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.088±0.071</t>
+          <t>-0.330±0.049</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.770±0.041</t>
+          <t>0.944±0.024</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.719±0.003</t>
+          <t>0.732±0.009</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>55.478±1.084</t>
+          <t>47.933±1.497</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>54.589±0.728</t>
+          <t>47.933±1.497</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>38.804±0.939</t>
+          <t>36.116±2.035</t>
         </is>
       </c>
     </row>
@@ -829,22 +891,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.3054 ± 0.0724</t>
+          <t>0.3742 ± 0.1203</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0655 ± 0.0203</t>
+          <t>0.0834 ± 0.0208</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.2693 ± 0.2696</t>
+          <t>1.6507 ± 0.4689</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>53.7886 ± 12.3747</t>
+          <t>64.1789 ± 20.8317</t>
         </is>
       </c>
     </row>
@@ -856,130 +918,130 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.1302 ± 0.0729</t>
+          <t>0.1295 ± 0.0356</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0268 ± 0.0351</t>
+          <t>0.0339 ± 0.0387</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.5453 ± 0.3035</t>
+          <t>0.5815 ± 0.1517</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>22.8827 ± 12.6197</t>
+          <t>22.1178 ± 5.5504</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mlotst</t>
+          <t>to</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.0640 ± 0.0441</t>
+          <t>0.0811 ± 0.0483</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0126 ± 0.0119</t>
+          <t>0.0240 ± 0.0187</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.2318 ± 0.1550</t>
+          <t>0.3760 ± 0.2203</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11.2954 ± 7.7646</t>
+          <t>13.8565 ± 8.2837</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>month_sin</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0629 ± 0.0346</t>
+          <t>0.0502 ± 0.0402</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0165 ± 0.0195</t>
+          <t>0.0171 ± 0.0134</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.2803 ± 0.1551</t>
+          <t>0.1960 ± 0.1675</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11.0549 ± 6.0236</t>
+          <t>8.5637 ± 6.9106</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>month_sin</t>
+          <t>month_cos</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.0428 ± 0.0271</t>
+          <t>0.0332 ± 0.0259</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0083 ± 0.0130</t>
+          <t>0.0048 ± 0.0102</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.1706 ± 0.1078</t>
+          <t>0.1243 ± 0.1061</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7.5265 ± 4.7585</t>
+          <t>5.6925 ± 4.4701</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>month_cos</t>
+          <t>mlotst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.0323 ± 0.0500</t>
+          <t>0.0151 ± 0.0295</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0003 ± 0.0068</t>
+          <t>0.0086 ± 0.0139</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.1215 ± 0.1803</t>
+          <t>0.0476 ± 0.1274</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5.7055 ± 8.8021</t>
+          <t>2.5206 ± 5.0000</t>
         </is>
       </c>
     </row>
@@ -991,22 +1053,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.0074 ± 0.0058</t>
+          <t>0.0140 ± 0.0184</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0001 ± 0.0074</t>
+          <t>0.0105 ± 0.0167</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.0286 ± 0.0225</t>
+          <t>0.0654 ± 0.0848</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.3133 ± 1.0266</t>
+          <t>2.3822 ± 3.1215</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M12"/>
+  <dimension ref="A2:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -1095,67 +1157,67 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.585±0.023</t>
+          <t>0.580±0.014</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.787±0.009</t>
+          <t>0.778±0.011</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.702±0.075</t>
+          <t>0.718±0.038</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.515±0.027</t>
+          <t>0.516±0.023</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.765±0.048</t>
+          <t>1.777±0.029</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.181±0.005</t>
+          <t>0.182±0.003</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.196±0.025</t>
+          <t>1.238±0.048</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.434±0.097</t>
+          <t>-0.352±0.074</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.929±0.036</t>
+          <t>0.958±0.061</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.739±0.006</t>
+          <t>0.731±0.008</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.033±0.867</t>
+          <t>47.800±1.573</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>48.033±0.867</t>
+          <t>47.800±1.573</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>34.417±0.937</t>
+          <t>35.246±1.504</t>
         </is>
       </c>
     </row>
@@ -1189,189 +1251,162 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>vgo</t>
+          <t>UGO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.1318 ± 0.0985</t>
+          <t>0.0746 ± 0.0636</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0265 ± 0.0333</t>
+          <t>-0.0089 ± 0.0315</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.6220 ± 0.4420</t>
+          <t>0.3240 ± 0.2752</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22.5579 ± 16.6627</t>
+          <t>12.9521 ± 11.3884</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ugo</t>
+          <t>VGO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.0809 ± 0.0488</t>
+          <t>0.0719 ± 0.0795</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.0052 ± 0.0208</t>
+          <t>0.0022 ± 0.0234</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.3841 ± 0.2238</t>
+          <t>0.3253 ± 0.3470</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.0094 ± 8.6379</t>
+          <t>12.3410 ± 13.7277</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mlotst</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.0578 ± 0.0341</t>
+          <t>0.0588 ± 0.0291</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0262 ± 0.0249</t>
+          <t>0.0066 ± 0.0198</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.2247 ± 0.1389</t>
+          <t>0.2634 ± 0.1311</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>9.8744 ± 5.8270</t>
+          <t>10.1243 ± 5.0319</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>MLOTST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0367 ± 0.0465</t>
+          <t>0.0571 ± 0.0326</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0086 ± 0.0148</t>
+          <t>0.0303 ± 0.0188</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.1775 ± 0.2235</t>
+          <t>0.2139 ± 0.1363</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6.4403 ± 8.4677</t>
+          <t>9.8893 ± 5.8053</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>month_cos</t>
+          <t>MSEN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.0153 ± 0.0251</t>
+          <t>0.0425 ± 0.0321</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0057 ± 0.0162</t>
+          <t>0.0110 ± 0.0171</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.0646 ± 0.1242</t>
+          <t>0.1717 ± 0.1371</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.5326 ± 4.2062</t>
+          <t>7.2996 ± 5.3532</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>month_sin</t>
+          <t>MCOS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.0090 ± 0.0181</t>
+          <t>0.0408 ± 0.0231</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0030 ± 0.0078</t>
+          <t>0.0171 ± 0.0325</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.0279 ± 0.0780</t>
+          <t>0.1523 ± 0.0889</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5779 ± 3.0943</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CDM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>0.0026 ± 0.0125</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0.0091 ± 0.0174</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0.0082 ± 0.0589</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.4034 ± 2.1578</t>
+          <t>7.0378 ± 3.9627</t>
         </is>
       </c>
     </row>
@@ -1460,67 +1495,67 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.421±0.030</t>
+          <t>0.369±0.184</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.651±0.024</t>
+          <t>0.595±0.192</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.766±0.035</t>
+          <t>0.603±0.385</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.249±0.037</t>
+          <t>0.223±0.053</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.287±0.032</t>
+          <t>1.397±0.181</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.099±0.002</t>
+          <t>0.122±0.016</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.702±0.030</t>
+          <t>0.754±0.072</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.023±0.064</t>
+          <t>-0.116±0.197</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.424±0.051</t>
+          <t>0.520±0.151</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.540±0.050</t>
+          <t>0.522±0.157</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>67.389±1.800</t>
+          <t>63.500±18.603</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>67.711±1.474</t>
+          <t>63.500±18.603</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>29.460±1.690</t>
+          <t>30.123±6.145</t>
         </is>
       </c>
     </row>
@@ -1559,76 +1594,76 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.1921 ± 0.0762</t>
+          <t>0.1734 ± 0.0794</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0312 ± 0.0255</t>
+          <t>0.0337 ± 0.0332</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.4208 ± 0.1508</t>
+          <t>0.3995 ± 0.1831</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>45.2020 ± 17.0786</t>
+          <t>40.7923 ± 18.4656</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>month_sin</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.1805 ± 0.2120</t>
+          <t>0.0762 ± 0.0540</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0824 ± 0.1172</t>
+          <t>0.0202 ± 0.0220</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.3679 ± 0.3560</t>
+          <t>0.1384 ± 0.0994</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>46.6456 ± 61.4460</t>
+          <t>17.9906 ± 12.3874</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>month_cos</t>
+          <t>to</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.1274 ± 0.1163</t>
+          <t>0.0646 ± 0.1565</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0510 ± 0.0396</t>
+          <t>0.0455 ± 0.0661</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.2610 ± 0.2332</t>
+          <t>0.1386 ± 0.3334</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>31.2075 ± 28.3798</t>
+          <t>13.2328 ± 34.0025</t>
         </is>
       </c>
     </row>
@@ -1640,49 +1675,49 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0975 ± 0.0618</t>
+          <t>0.0571 ± 0.0441</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0274 ± 0.0252</t>
+          <t>0.0036 ± 0.0261</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.2131 ± 0.1271</t>
+          <t>0.1225 ± 0.0912</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>24.1522 ± 17.7990</t>
+          <t>12.9515 ± 8.6282</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>month_sin</t>
+          <t>month_cos</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.0688 ± 0.0309</t>
+          <t>0.0412 ± 0.1082</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0163 ± 0.0210</t>
+          <t>0.0412 ± 0.0450</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.1411 ± 0.0641</t>
+          <t>0.0977 ± 0.2369</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>16.6958 ± 8.0690</t>
+          <t>7.9902 ± 23.7439</t>
         </is>
       </c>
     </row>
@@ -1694,22 +1729,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.0438 ± 0.0511</t>
+          <t>-0.0065 ± 0.0357</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0074 ± 0.0176</t>
+          <t>0.0036 ± 0.0195</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.1132 ± 0.1177</t>
+          <t>0.0046 ± 0.0902</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10.0123 ± 11.7731</t>
+          <t>-1.9827 ± 8.7039</t>
         </is>
       </c>
     </row>
@@ -1721,22 +1756,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.0046 ± 0.0138</t>
+          <t>-0.0215 ± 0.0245</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0208 ± 0.0171</t>
+          <t>0.0169 ± 0.0232</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.0195 ± 0.0279</t>
+          <t>-0.0384 ± 0.0459</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.3146 ± 3.7783</t>
+          <t>-5.2397 ± 6.0503</t>
         </is>
       </c>
     </row>
@@ -1752,6 +1787,344 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A2:M11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>pearson_corr</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>r2_plot</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>mean_ssim</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>rmse</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>nrmse</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>mae</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>mbe</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>w_dist</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>spearman_corr</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>hit_rate_percent</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>mean_yearly_hit_rate</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>mean_monthly_hit_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0.461±0.047</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.682±0.034</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.766±0.040</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.221±0.025</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.300±0.057</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.113±0.005</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.732±0.031</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-0.050±0.079</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.436±0.030</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.636±0.024</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>68.867±2.691</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>68.867±2.691</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>35.265±1.896</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>variable</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>r2_importance</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>ssim_importance</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>loss_importance</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>r2_drop_%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VGO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.1027 ± 0.0308</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.0138 ± 0.0209</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.2014 ± 0.0613</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>22.3837 ± 6.8176</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MSEN</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.0910 ± 0.0993</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.0067 ± 0.0281</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.1752 ± 0.1951</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>19.3395 ± 21.2809</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.0662 ± 0.0791</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.0284 ± 0.0455</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.1416 ± 0.1530</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>14.9768 ± 18.6829</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>UGO</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.0365 ± 0.0233</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.0130 ± 0.0077</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.0802 ± 0.0466</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7.8126 ± 4.3482</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MCOS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.0342 ± 0.0528</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.0208 ± 0.0552</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.0709 ± 0.0985</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>7.5836 ± 11.5442</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MLOTST</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>-0.0121 ± 0.0442</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.0248 ± 0.0336</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-0.0061 ± 0.0956</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-2.9130 ± 10.4762</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A2:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1825,67 +2198,67 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.435±0.025</t>
+          <t>0.438±0.030</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.671±0.018</t>
+          <t>0.665±0.022</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.715±0.050</t>
+          <t>0.759±0.038</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.236±0.039</t>
+          <t>0.219±0.023</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.332±0.029</t>
+          <t>1.328±0.036</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.116±0.003</t>
+          <t>0.115±0.003</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.721±0.030</t>
+          <t>0.743±0.026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.109±0.073</t>
+          <t>-0.056±0.077</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.492±0.036</t>
+          <t>0.444±0.034</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.594±0.052</t>
+          <t>0.613±0.041</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>69.233±1.846</t>
+          <t>67.933±1.884</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>69.233±1.846</t>
+          <t>67.933±1.884</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>33.340±2.222</t>
+          <t>34.675±1.230</t>
         </is>
       </c>
     </row>
@@ -1919,162 +2292,162 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>vgo</t>
+          <t>MCOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.1103 ± 0.0342</t>
+          <t>0.2194 ± 0.2259</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0128 ± 0.0194</t>
+          <t>0.0582 ± 0.0780</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.2639 ± 0.0653</t>
+          <t>0.4339 ± 0.4355</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.3463 ± 7.5066</t>
+          <t>49.6649 ± 52.0636</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>month_sin</t>
+          <t>VGO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.0687 ± 0.0553</t>
+          <t>0.1979 ± 0.0504</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0088 ± 0.0134</t>
+          <t>0.0329 ± 0.0303</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.1426 ± 0.1160</t>
+          <t>0.4032 ± 0.1004</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15.6653 ± 12.4544</t>
+          <t>45.2172 ± 11.5505</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>MSEN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.0547 ± 0.0663</t>
+          <t>0.0991 ± 0.0467</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0464 ± 0.0601</t>
+          <t>0.0129 ± 0.0209</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.0920 ± 0.1583</t>
+          <t>0.1854 ± 0.0924</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12.4504 ± 14.7083</t>
+          <t>22.6222 ± 10.2300</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>month_cos</t>
+          <t>UGO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0478 ± 0.0447</t>
+          <t>0.0658 ± 0.0399</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0100 ± 0.0220</t>
+          <t>0.0080 ± 0.0212</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.0848 ± 0.0821</t>
+          <t>0.1380 ± 0.0786</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11.1414 ± 10.2741</t>
+          <t>14.6720 ± 8.3084</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ugo</t>
+          <t>MLOTST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.0367 ± 0.0396</t>
+          <t>0.0151 ± 0.0693</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0020 ± 0.0121</t>
+          <t>0.0102 ± 0.0183</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.0885 ± 0.0854</t>
+          <t>0.0743 ± 0.1390</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8.6130 ± 9.3178</t>
+          <t>3.0196 ± 15.3673</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mlotst</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-0.0227 ± 0.0485</t>
+          <t>0.0132 ± 0.0694</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0211 ± 0.0263</t>
+          <t>0.0429 ± 0.0591</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.0028 ± 0.1238</t>
+          <t>0.0404 ± 0.1352</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-5.4246 ± 11.2706</t>
+          <t>2.4329 ± 15.8562</t>
         </is>
       </c>
     </row>
@@ -2086,22 +2459,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-0.0271 ± 0.0229</t>
+          <t>-0.0295 ± 0.0320</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0111 ± 0.0235</t>
+          <t>0.0052 ± 0.0150</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-0.0533 ± 0.0464</t>
+          <t>-0.0485 ± 0.0515</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-6.2919 ± 5.3649</t>
+          <t>-6.9366 ± 7.4598</t>
         </is>
       </c>
     </row>

--- a/modelado/modelos/resultados/Regre/DL_reg.xlsx
+++ b/modelado/modelos/resultados/Regre/DL_reg.xlsx
@@ -3,31 +3,38 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="StackedCNN3D_HKP" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="UNet3D_HKP" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="StackedCNN3D_SQA" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="UNet3D_SQA" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="CNN3D_SQA" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="UNet3D_HKP" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="UNet3D_SQA" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="CNN3D_SQA" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="UNet3D_SQA_todas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="CNN3D_HKP" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="UNet3D_HKP_todas" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="CNN3D_HKP_todas" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -41,12 +48,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -59,9 +81,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -149,6 +174,201 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="9344025" cy="2847975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8058150" cy="2990850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9420225" cy="2847975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8172450" cy="2990850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9420225" cy="2847975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8172450" cy="2990850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="9420225" cy="2847975"/>
     <pic>
       <nvPicPr>
@@ -177,7 +397,7 @@
       <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8058150" cy="2990850"/>
+    <ext cx="8172450" cy="2990850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -201,7 +421,72 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9420225" cy="2847975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8058150" cy="2990850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -262,7 +547,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -271,68 +556,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9420225" cy="2847975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>13</col>
-      <colOff>0</colOff>
-      <row>19</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="8172450" cy="2990850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>13</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="9420225" cy="2847975"/>
+    <ext cx="9410700" cy="2847975"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -357,7 +581,7 @@
       <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8172450" cy="2990850"/>
+    <ext cx="8058150" cy="2990850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -371,67 +595,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>13</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="9420225" cy="2847975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>13</col>
-      <colOff>0</colOff>
-      <row>19</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="8172450" cy="2990850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -707,7 +870,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -719,8 +882,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A2:M11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -792,7 +955,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.584±0.017</t>
+          <t>0.580±0.014</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -802,57 +965,57 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.714±0.040</t>
+          <t>0.718±0.038</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.517±0.023</t>
+          <t>0.516±0.023</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.768±0.037</t>
+          <t>1.777±0.029</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.181±0.004</t>
+          <t>0.182±0.003</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.226±0.026</t>
+          <t>1.238±0.048</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.330±0.049</t>
+          <t>-0.352±0.074</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.944±0.024</t>
+          <t>0.958±0.061</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.732±0.009</t>
+          <t>0.731±0.008</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>47.933±1.497</t>
+          <t>47.800±1.573</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>47.933±1.497</t>
+          <t>47.800±1.573</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>36.116±2.035</t>
+          <t>35.246±1.504</t>
         </is>
       </c>
     </row>
@@ -886,189 +1049,162 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>vgo</t>
+          <t>UGO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.3742 ± 0.1203</t>
+          <t>0.0746 ± 0.0636</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0834 ± 0.0208</t>
+          <t>-0.0089 ± 0.0315</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.6507 ± 0.4689</t>
+          <t>0.3240 ± 0.2752</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>64.1789 ± 20.8317</t>
+          <t>12.9521 ± 11.3884</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ugo</t>
+          <t>VGO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.1295 ± 0.0356</t>
+          <t>0.0719 ± 0.0795</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0339 ± 0.0387</t>
+          <t>0.0022 ± 0.0234</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.5815 ± 0.1517</t>
+          <t>0.3253 ± 0.3470</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>22.1178 ± 5.5504</t>
+          <t>12.3410 ± 13.7277</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.0811 ± 0.0483</t>
+          <t>0.0588 ± 0.0291</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0240 ± 0.0187</t>
+          <t>0.0066 ± 0.0198</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.3760 ± 0.2203</t>
+          <t>0.2634 ± 0.1311</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13.8565 ± 8.2837</t>
+          <t>10.1243 ± 5.0319</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>month_sin</t>
+          <t>MLOTST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0502 ± 0.0402</t>
+          <t>0.0571 ± 0.0326</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0171 ± 0.0134</t>
+          <t>0.0303 ± 0.0188</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.1960 ± 0.1675</t>
+          <t>0.2139 ± 0.1363</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8.5637 ± 6.9106</t>
+          <t>9.8893 ± 5.8053</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>month_cos</t>
+          <t>MSEN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.0332 ± 0.0259</t>
+          <t>0.0425 ± 0.0321</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0048 ± 0.0102</t>
+          <t>0.0110 ± 0.0171</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.1243 ± 0.1061</t>
+          <t>0.1717 ± 0.1371</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5.6925 ± 4.4701</t>
+          <t>7.2996 ± 5.3532</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mlotst</t>
+          <t>MCOS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.0151 ± 0.0295</t>
+          <t>0.0408 ± 0.0231</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0086 ± 0.0139</t>
+          <t>0.0171 ± 0.0325</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.0476 ± 0.1274</t>
+          <t>0.1523 ± 0.0889</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.5206 ± 5.0000</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CDM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>0.0140 ± 0.0184</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0.0105 ± 0.0167</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0.0654 ± 0.0848</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2.3822 ± 3.1215</t>
+          <t>7.0378 ± 3.9627</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1221,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A2:M11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -1157,67 +1293,67 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.580±0.014</t>
+          <t>0.470±0.016</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.778±0.011</t>
+          <t>0.689±0.012</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.718±0.038</t>
+          <t>0.777±0.019</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.516±0.023</t>
+          <t>0.217±0.019</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.777±0.029</t>
+          <t>1.291±0.019</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.182±0.003</t>
+          <t>0.112±0.002</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.238±0.048</t>
+          <t>0.725±0.018</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.352±0.074</t>
+          <t>-0.070±0.058</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.958±0.061</t>
+          <t>0.429±0.043</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.731±0.008</t>
+          <t>0.640±0.016</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>47.800±1.573</t>
+          <t>69.267±1.776</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>47.800±1.573</t>
+          <t>69.267±1.776</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>35.246±1.504</t>
+          <t>34.751±1.324</t>
         </is>
       </c>
     </row>
@@ -1251,162 +1387,162 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UGO</t>
+          <t>VGO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.0746 ± 0.0636</t>
+          <t>0.1467 ± 0.0752</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.0089 ± 0.0315</t>
+          <t>0.0206 ± 0.0224</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.3240 ± 0.2752</t>
+          <t>0.2815 ± 0.1427</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12.9521 ± 11.3884</t>
+          <t>31.4434 ± 16.6670</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VGO</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.0719 ± 0.0795</t>
+          <t>0.1090 ± 0.1405</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0022 ± 0.0234</t>
+          <t>0.0304 ± 0.0440</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.3253 ± 0.3470</t>
+          <t>0.2152 ± 0.2637</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12.3410 ± 13.7277</t>
+          <t>23.3145 ± 30.5374</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MSEN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.0588 ± 0.0291</t>
+          <t>0.1006 ± 0.1071</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0066 ± 0.0198</t>
+          <t>-0.0012 ± 0.0207</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.2634 ± 0.1311</t>
+          <t>0.1865 ± 0.1925</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10.1243 ± 5.0319</t>
+          <t>21.2878 ± 23.0369</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MLOTST</t>
+          <t>MCOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0571 ± 0.0326</t>
+          <t>0.0968 ± 0.1591</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0303 ± 0.0188</t>
+          <t>0.0344 ± 0.0570</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.2139 ± 0.1363</t>
+          <t>0.2049 ± 0.2983</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>9.8893 ± 5.8053</t>
+          <t>20.8142 ± 34.2161</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MSEN</t>
+          <t>UGO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.0425 ± 0.0321</t>
+          <t>0.0323 ± 0.0216</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0110 ± 0.0171</t>
+          <t>0.0068 ± 0.0152</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.1717 ± 0.1371</t>
+          <t>0.0646 ± 0.0402</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7.2996 ± 5.3532</t>
+          <t>6.9294 ± 4.7911</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MCOS</t>
+          <t>MLOTST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.0408 ± 0.0231</t>
+          <t>0.0024 ± 0.0561</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0171 ± 0.0325</t>
+          <t>0.0432 ± 0.0362</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.1523 ± 0.0889</t>
+          <t>0.0242 ± 0.1157</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7.0378 ± 3.9627</t>
+          <t>0.3907 ± 11.9671</t>
         </is>
       </c>
     </row>
@@ -1422,8 +1558,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A2:M11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -1495,67 +1631,67 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.369±0.184</t>
+          <t>0.448±0.019</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.595±0.192</t>
+          <t>0.675±0.019</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.603±0.385</t>
+          <t>0.759±0.023</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.223±0.053</t>
+          <t>0.215±0.027</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.397±0.181</t>
+          <t>1.317±0.023</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.122±0.016</t>
+          <t>0.115±0.002</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.754±0.072</t>
+          <t>0.725±0.014</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.116±0.197</t>
+          <t>-0.082±0.089</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.520±0.151</t>
+          <t>0.425±0.031</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.522±0.157</t>
+          <t>0.631±0.024</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>63.500±18.603</t>
+          <t>69.333±1.457</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>63.500±18.603</t>
+          <t>69.333±1.457</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>30.123±6.145</t>
+          <t>34.194±1.953</t>
         </is>
       </c>
     </row>
@@ -1589,189 +1725,162 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>vgo</t>
+          <t>MSEN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.1734 ± 0.0794</t>
+          <t>0.1886 ± 0.1014</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0337 ± 0.0332</t>
+          <t>0.0275 ± 0.0372</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.3995 ± 0.1831</t>
+          <t>0.3402 ± 0.1873</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>40.7923 ± 18.4656</t>
+          <t>41.4646 ± 20.7782</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>month_sin</t>
+          <t>VGO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.0762 ± 0.0540</t>
+          <t>0.1831 ± 0.0334</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0202 ± 0.0220</t>
+          <t>0.0287 ± 0.0109</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.1384 ± 0.0994</t>
+          <t>0.3606 ± 0.0639</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17.9906 ± 12.3874</t>
+          <t>40.9487 ± 7.7714</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>MCOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.0646 ± 0.1565</t>
+          <t>0.1452 ± 0.2128</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0455 ± 0.0661</t>
+          <t>0.0384 ± 0.0662</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.1386 ± 0.3334</t>
+          <t>0.3258 ± 0.4068</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13.2328 ± 34.0025</t>
+          <t>32.5486 ± 47.2738</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ugo</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0571 ± 0.0441</t>
+          <t>0.0967 ± 0.1238</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0036 ± 0.0261</t>
+          <t>0.0828 ± 0.0683</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.1225 ± 0.0912</t>
+          <t>0.2345 ± 0.2703</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12.9515 ± 8.6282</t>
+          <t>22.1968 ± 28.5631</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>month_cos</t>
+          <t>UGO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.0412 ± 0.1082</t>
+          <t>0.0682 ± 0.0279</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0412 ± 0.0450</t>
+          <t>0.0154 ± 0.0128</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.0977 ± 0.2369</t>
+          <t>0.1451 ± 0.0564</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7.9902 ± 23.7439</t>
+          <t>15.1591 ± 5.9709</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mlotst</t>
+          <t>MLOTST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-0.0065 ± 0.0357</t>
+          <t>-0.0023 ± 0.0516</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0036 ± 0.0195</t>
+          <t>0.0161 ± 0.0240</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.0046 ± 0.0902</t>
+          <t>0.0090 ± 0.0967</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-1.9827 ± 8.7039</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CDM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>-0.0215 ± 0.0245</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0.0169 ± 0.0232</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>-0.0384 ± 0.0459</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>-5.2397 ± 6.0503</t>
+          <t>-0.6715 ± 11.5423</t>
         </is>
       </c>
     </row>
@@ -1787,71 +1896,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M11"/>
+  <dimension ref="A2:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>r2</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>pearson_corr</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>r2_plot</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>mean_ssim</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>rmse</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>nrmse</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>mae</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>mbe</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>w_dist</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>spearman_corr</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>hit_rate_percent</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>mean_yearly_hit_rate</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>mean_monthly_hit_rate</t>
         </is>
@@ -1860,92 +1969,92 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.461±0.047</t>
+          <t>0.428±0.033</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.682±0.034</t>
+          <t>0.663±0.024</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.766±0.040</t>
+          <t>0.747±0.043</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.221±0.025</t>
+          <t>0.202±0.020</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.300±0.057</t>
+          <t>1.340±0.038</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.113±0.005</t>
+          <t>0.116±0.003</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.732±0.031</t>
+          <t>0.751±0.026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.050±0.079</t>
+          <t>-0.100±0.064</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.436±0.030</t>
+          <t>0.457±0.049</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.636±0.024</t>
+          <t>0.616±0.040</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>68.867±2.691</t>
+          <t>67.333±2.293</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>68.867±2.691</t>
+          <t>67.333±2.293</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>35.265±1.896</t>
+          <t>33.382±1.761</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>r2_importance</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>ssim_importance</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>loss_importance</t>
         </is>
       </c>
-      <c r="E5" s="1" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>r2_drop_%</t>
         </is>
@@ -1954,162 +2063,243 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VGO</t>
+          <t>MSEN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.1027 ± 0.0308</t>
+          <t>0.0895 ± 0.0691</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0138 ± 0.0209</t>
+          <t>0.0242 ± 0.0334</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.2014 ± 0.0613</t>
+          <t>0.1613 ± 0.1358</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22.3837 ± 6.8176</t>
+          <t>21.3644 ± 17.0255</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MSEN</t>
+          <t>VGO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.0910 ± 0.0993</t>
+          <t>0.0887 ± 0.0471</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0067 ± 0.0281</t>
+          <t>0.0120 ± 0.0129</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.1752 ± 0.1951</t>
+          <t>0.1696 ± 0.0967</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19.3395 ± 21.2809</t>
+          <t>20.7269 ± 11.0094</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>UGO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.0662 ± 0.0791</t>
+          <t>0.0294 ± 0.0229</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0284 ± 0.0455</t>
+          <t>-0.0028 ± 0.0081</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.1416 ± 0.1530</t>
+          <t>0.0569 ± 0.0460</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14.9768 ± 18.6829</t>
+          <t>7.1677 ± 5.9339</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UGO</t>
+          <t>MLOTST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0365 ± 0.0233</t>
+          <t>0.0260 ± 0.0505</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0130 ± 0.0077</t>
+          <t>0.0334 ± 0.0287</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.0802 ± 0.0466</t>
+          <t>0.0609 ± 0.1011</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7.8126 ± 4.3482</t>
+          <t>5.6306 ± 11.0047</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MCOS</t>
+          <t>CHL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.0342 ± 0.0528</t>
+          <t>0.0114 ± 0.0259</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0208 ± 0.0552</t>
+          <t>0.0078 ± 0.0094</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.0709 ± 0.0985</t>
+          <t>0.0275 ± 0.0468</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7.5836 ± 11.5442</t>
+          <t>2.5848 ± 5.9369</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MLOTST</t>
+          <t>CDM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-0.0121 ± 0.0442</t>
+          <t>-0.0019 ± 0.0323</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0248 ± 0.0336</t>
+          <t>0.0155 ± 0.0177</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.0061 ± 0.0956</t>
+          <t>0.0014 ± 0.0626</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-2.9130 ± 10.4762</t>
+          <t>-0.4713 ± 7.7563</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>-0.0099 ± 0.0311</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0.0301 ± 0.0370</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-0.0158 ± 0.0569</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>-2.2234 ± 7.4182</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SPM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>-0.0159 ± 0.0218</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-0.0156 ± 0.0212</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-0.0301 ± 0.0416</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-3.8553 ± 5.1326</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MCOS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>-0.0199 ± 0.0519</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.0203 ± 0.0194</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>-0.0272 ± 0.1233</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>-4.9184 ± 11.8670</t>
         </is>
       </c>
     </row>
@@ -2125,71 +2315,409 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M12"/>
+  <dimension ref="A2:M11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>pearson_corr</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>r2_plot</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>mean_ssim</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>rmse</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>nrmse</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>mae</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>mbe</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>w_dist</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>spearman_corr</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>hit_rate_percent</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>mean_yearly_hit_rate</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>mean_monthly_hit_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0.561±0.014</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.764±0.006</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.676±0.065</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.507±0.013</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.815±0.029</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.186±0.003</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1.261±0.034</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-0.344±0.077</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.950±0.048</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.720±0.005</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>47.933±1.438</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>47.933±1.438</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>36.145±0.968</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>variable</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>r2_importance</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>ssim_importance</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>loss_importance</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>r2_drop_%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VGO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.3916 ± 0.1628</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.0830 ± 0.0354</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1.6238 ± 0.6345</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>69.8766 ± 29.5987</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.1135 ± 0.0907</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.0181 ± 0.0306</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.4995 ± 0.3911</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20.3015 ± 16.3959</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>UGO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.0944 ± 0.0249</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.0070 ± 0.0254</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.3958 ± 0.1050</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>16.7907 ± 4.3739</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MSEN</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.0897 ± 0.0720</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.0121 ± 0.0153</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.3621 ± 0.2975</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>15.9424 ± 12.8202</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MCOS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.0756 ± 0.0566</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.0081 ± 0.0242</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.2994 ± 0.2426</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>13.6083 ± 10.1639</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MLOTST</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.0557 ± 0.0390</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.0095 ± 0.0182</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.2064 ± 0.1551</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>9.9008 ± 6.9630</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>r2</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>pearson_corr</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>r2_plot</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>mean_ssim</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>rmse</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>nrmse</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>mae</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>mbe</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>w_dist</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>spearman_corr</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>hit_rate_percent</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>mean_yearly_hit_rate</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>mean_monthly_hit_rate</t>
         </is>
@@ -2198,92 +2726,92 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.438±0.030</t>
+          <t>0.585±0.020</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.665±0.022</t>
+          <t>0.781±0.016</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.759±0.038</t>
+          <t>0.752±0.053</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.219±0.023</t>
+          <t>0.525±0.014</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.328±0.036</t>
+          <t>1.766±0.042</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.115±0.003</t>
+          <t>0.181±0.004</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.743±0.026</t>
+          <t>1.231±0.040</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.056±0.077</t>
+          <t>-0.355±0.071</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.444±0.034</t>
+          <t>0.952±0.044</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.613±0.041</t>
+          <t>0.733±0.013</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>67.933±1.884</t>
+          <t>47.833±1.468</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>67.933±1.884</t>
+          <t>47.833±1.468</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>34.675±1.230</t>
+          <t>34.539±1.854</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>r2_importance</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>ssim_importance</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>loss_importance</t>
         </is>
       </c>
-      <c r="E5" s="1" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>r2_drop_%</t>
         </is>
@@ -2292,189 +2820,662 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MCOS</t>
+          <t>VGO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.2194 ± 0.2259</t>
+          <t>0.1032 ± 0.1489</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0582 ± 0.0780</t>
+          <t>0.0208 ± 0.0468</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.4339 ± 0.4355</t>
+          <t>0.4395 ± 0.6166</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>49.6649 ± 52.0636</t>
+          <t>17.5208 ± 25.1148</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VGO</t>
+          <t>UGO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.1979 ± 0.0504</t>
+          <t>0.0805 ± 0.0462</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0329 ± 0.0303</t>
+          <t>0.0005 ± 0.0278</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.4032 ± 0.1004</t>
+          <t>0.3470 ± 0.1951</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>45.2172 ± 11.5505</t>
+          <t>13.7010 ± 7.8044</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MSEN</t>
+          <t>SPM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.0991 ± 0.0467</t>
+          <t>0.0503 ± 0.0434</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0129 ± 0.0209</t>
+          <t>0.0166 ± 0.0214</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.1854 ± 0.0924</t>
+          <t>0.2238 ± 0.1918</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>22.6222 ± 10.2300</t>
+          <t>8.5258 ± 7.3458</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UGO</t>
+          <t>MLOTST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0658 ± 0.0399</t>
+          <t>0.0226 ± 0.0209</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0080 ± 0.0212</t>
+          <t>0.0196 ± 0.0237</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.1380 ± 0.0786</t>
+          <t>0.0753 ± 0.0864</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>14.6720 ± 8.3084</t>
+          <t>3.7978 ± 3.4835</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MLOTST</t>
+          <t>MSEN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.0151 ± 0.0693</t>
+          <t>0.0223 ± 0.0243</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0102 ± 0.0183</t>
+          <t>0.0221 ± 0.0225</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.0743 ± 0.1390</t>
+          <t>0.0803 ± 0.0965</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.0196 ± 15.3673</t>
+          <t>3.7809 ± 4.0769</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MCOS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.0132 ± 0.0694</t>
+          <t>0.0122 ± 0.0279</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0429 ± 0.0591</t>
+          <t>0.0165 ± 0.0190</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.0404 ± 0.1352</t>
+          <t>0.0421 ± 0.1108</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.4329 ± 15.8562</t>
+          <t>2.1410 ± 5.0316</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.0091 ± 0.0141</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-0.0026 ± 0.0065</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.0399 ± 0.0633</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.5446 ± 2.4082</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>CDM</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0.0067 ± 0.0109</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0.0068 ± 0.0050</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.0277 ± 0.0481</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.1675 ± 1.8962</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CHL</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0.0043 ± 0.0174</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.0025 ± 0.0159</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.0154 ± 0.0755</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0.7223 ± 2.9674</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:M14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>pearson_corr</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>r2_plot</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>mean_ssim</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>rmse</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>nrmse</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>mae</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>mbe</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>w_dist</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>spearman_corr</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>hit_rate_percent</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>mean_yearly_hit_rate</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>mean_monthly_hit_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0.579±0.016</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.777±0.008</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.716±0.051</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.521±0.018</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.778±0.035</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.182±0.004</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1.220±0.033</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-0.362±0.086</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.934±0.049</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.730±0.005</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>47.933±1.404</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>47.933±1.404</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>35.535±1.415</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>variable</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>r2_importance</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>ssim_importance</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>loss_importance</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>r2_drop_%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VGO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.3751 ± 0.1709</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.0797 ± 0.0388</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1.5510 ± 0.6489</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>65.2179 ± 30.8706</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>UGO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.1198 ± 0.0466</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.0177 ± 0.0245</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.5075 ± 0.1934</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20.7504 ± 8.4369</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.0829 ± 0.0489</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.0146 ± 0.0125</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.3639 ± 0.2099</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>14.2740 ± 8.2364</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MSEN</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.0554 ± 0.0496</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.0095 ± 0.0115</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.2281 ± 0.2097</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>9.5484 ± 8.5662</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MLOTST</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.0516 ± 0.0450</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.0135 ± 0.0106</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.2068 ± 0.1828</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8.8428 ± 7.6337</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MCOS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.0347 ± 0.0265</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.0018 ± 0.0077</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.1350 ± 0.1008</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>5.9437 ± 4.4721</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SPM</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-0.0295 ± 0.0320</t>
+          <t>0.0212 ± 0.0144</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0052 ± 0.0150</t>
+          <t>0.0001 ± 0.0058</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-0.0485 ± 0.0515</t>
+          <t>0.0930 ± 0.0648</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-6.9366 ± 7.4598</t>
+          <t>3.6551 ± 2.4864</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CHL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0.0052 ± 0.0173</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0.0023 ± 0.0093</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.0238 ± 0.0725</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.8792 ± 3.0533</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0.0020 ± 0.0169</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-0.0009 ± 0.0094</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.0068 ± 0.0706</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0.2888 ± 2.8484</t>
         </is>
       </c>
     </row>

--- a/modelado/modelos/resultados/Regre/DL_reg.xlsx
+++ b/modelado/modelos/resultados/Regre/DL_reg.xlsx
@@ -14,6 +14,7 @@
     <sheet name="CNN3D_HKP" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="UNet3D_HKP_todas" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="CNN3D_HKP_todas" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="UNet3DReg_SQA" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -570,6 +571,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -589,6 +593,39 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9420225" cy="2847975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3483,4 +3520,312 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:J11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>pearson_corr</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>r2_plot</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>mean_ssim</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>rmse</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>nrmse</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>mae</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>mbe</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>w_dist</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>spearman_corr</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0.460±0.033</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.684±0.027</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.764±0.041</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.209±0.023</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.301±0.040</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.113±0.004</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.731±0.017</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-0.061±0.053</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.455±0.040</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.635±0.023</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>variable</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>r2_importance</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>ssim_importance</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>loss_importance</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>r2_drop_%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MSEN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.1282 ± 0.0561</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.0413 ± 0.0475</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.2387 ± 0.1160</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>27.8180 ± 12.2491</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>VGO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.1024 ± 0.0544</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.0084 ± 0.0175</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.1976 ± 0.1014</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>22.0147 ± 10.9738</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.1010 ± 0.1495</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.0564 ± 0.0319</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.2047 ± 0.2939</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>20.6779 ± 29.1840</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MCOS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.0698 ± 0.1275</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.0716 ± 0.0838</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.1435 ± 0.2648</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>16.2821 ± 29.5147</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>UGO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.0246 ± 0.0177</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-0.0015 ± 0.0123</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.0501 ± 0.0351</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>5.2377 ± 3.7982</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MLOTST</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.0161 ± 0.0371</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.0286 ± 0.0255</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.0511 ± 0.0887</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3.8142 ± 7.9278</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/modelado/modelos/resultados/Regre/DL_reg.xlsx
+++ b/modelado/modelos/resultados/Regre/DL_reg.xlsx
@@ -15,6 +15,7 @@
     <sheet name="UNet3D_HKP_todas" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="CNN3D_HKP_todas" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="UNet3DReg_SQA" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="UNet3DReg_HKP" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -639,6 +640,39 @@
 </wsDr>
 </file>
 
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9344025" cy="2847975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -913,6 +947,314 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:J11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>pearson_corr</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>r2_plot</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>mean_ssim</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>rmse</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>nrmse</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>mae</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>mbe</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>w_dist</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>spearman_corr</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0.610±0.013</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.789±0.005</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.765±0.038</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.545±0.014</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.711±0.028</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.175±0.003</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1.176±0.044</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-0.250±0.059</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.867±0.055</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.734±0.003</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>variable</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>r2_importance</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>ssim_importance</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>loss_importance</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>r2_drop_%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>UGO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.1243 ± 0.1536</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-0.0053 ± 0.0153</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.5224 ± 0.6389</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>20.1016 ± 24.7442</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.1056 ± 0.0051</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.0384 ± 0.0193</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.4614 ± 0.0172</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>17.3126 ± 1.2011</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MLOTST</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.0752 ± 0.0612</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.0060 ± 0.0066</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.2914 ± 0.2422</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>12.2147 ± 9.7625</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>VGO</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.0403 ± 0.0031</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.0058 ± 0.0037</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.1899 ± 0.0275</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>6.6042 ± 0.6446</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MCOS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.0371 ± 0.0098</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.0089 ± 0.0045</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.1462 ± 0.0306</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>6.0567 ± 1.4711</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MSEN</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.0147 ± 0.0111</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.0100 ± 0.0100</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.0548 ± 0.0394</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2.4357 ± 1.8761</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -3528,7 +3870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:J11"/>
+  <dimension ref="A2:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -3544,40 +3886,35 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>r2_plot</t>
+          <t>mean_ssim</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>mean_ssim</t>
+          <t>rmse</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>rmse</t>
+          <t>nrmse</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>nrmse</t>
+          <t>mae</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>mae</t>
+          <t>mbe</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>mbe</t>
+          <t>w_dist</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>w_dist</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>spearman_corr</t>
         </is>
@@ -3586,52 +3923,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.460±0.033</t>
+          <t>0.423±0.001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.684±0.027</t>
+          <t>0.658±0.003</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.764±0.041</t>
+          <t>0.177±0.016</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.209±0.023</t>
+          <t>1.347±0.001</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.301±0.040</t>
+          <t>0.117±0.000</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.113±0.004</t>
+          <t>0.723±0.016</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.731±0.017</t>
+          <t>-0.139±0.014</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.061±0.053</t>
+          <t>0.473±0.001</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.455±0.040</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.635±0.023</t>
+          <t>0.612±0.063</t>
         </is>
       </c>
     </row>
@@ -3665,54 +3997,54 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MSEN</t>
+          <t>MCOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.1282 ± 0.0561</t>
+          <t>0.1928 ± 0.1729</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0413 ± 0.0475</t>
+          <t>0.1226 ± 0.1012</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.2387 ± 0.1160</t>
+          <t>0.3436 ± 0.4426</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27.8180 ± 12.2491</t>
+          <t>45.6293 ± 40.9636</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VGO</t>
+          <t>UGO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.1024 ± 0.0544</t>
+          <t>0.0759 ± 0.0188</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0084 ± 0.0175</t>
+          <t>0.0053 ± 0.0045</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.1976 ± 0.1014</t>
+          <t>0.1358 ± 0.0357</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>22.0147 ± 10.9738</t>
+          <t>17.9600 ± 4.4642</t>
         </is>
       </c>
     </row>
@@ -3724,103 +4056,157 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.1010 ± 0.1495</t>
+          <t>0.0580 ± 0.0878</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0564 ± 0.0319</t>
+          <t>0.0156 ± 0.0219</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.2047 ± 0.2939</t>
+          <t>0.0996 ± 0.1688</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20.6779 ± 29.1840</t>
+          <t>13.7172 ± 20.7582</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MCOS</t>
+          <t>MSEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0698 ± 0.1275</t>
+          <t>0.0531 ± 0.0375</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0716 ± 0.0838</t>
+          <t>0.0468 ± 0.0690</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.1435 ± 0.2648</t>
+          <t>0.0842 ± 0.0876</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>16.2821 ± 29.5147</t>
+          <t>12.5638 ± 8.8911</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UGO</t>
+          <t>MLOTST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.0246 ± 0.0177</t>
+          <t>0.0426 ± 0.0257</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.0015 ± 0.0123</t>
+          <t>0.0283 ± 0.0223</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.0501 ± 0.0351</t>
+          <t>0.0771 ± 0.0320</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5.2377 ± 3.7982</t>
+          <t>10.0754 ± 6.0885</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MLOTST</t>
+          <t>VGO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.0161 ± 0.0371</t>
+          <t>0.0335 ± 0.0412</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0286 ± 0.0255</t>
+          <t>0.0013 ± 0.0034</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.0511 ± 0.0887</t>
+          <t>0.0645 ± 0.0869</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.8142 ± 7.9278</t>
+          <t>7.9206 ± 9.7360</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TOB</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.0187 ± 0.0126</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0.0096 ± 0.0117</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.0339 ± 0.0266</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>4.4120 ± 2.9653</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SO</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0.0113 ± 0.0025</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-0.0156 ± 0.0008</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.0237 ± 0.0079</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2.6807 ± 0.5871</t>
         </is>
       </c>
     </row>

--- a/modelado/modelos/resultados/Regre/DL_reg.xlsx
+++ b/modelado/modelos/resultados/Regre/DL_reg.xlsx
@@ -3870,7 +3870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:I13"/>
+  <dimension ref="A2:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -3923,47 +3923,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.423±0.001</t>
+          <t>0.438±0.060</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.658±0.003</t>
+          <t>0.669±0.038</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.177±0.016</t>
+          <t>0.149±0.045</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.347±0.001</t>
+          <t>1.328±0.071</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.117±0.000</t>
+          <t>0.115±0.006</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.723±0.016</t>
+          <t>0.744±0.074</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.139±0.014</t>
+          <t>-0.140±0.082</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.473±0.001</t>
+          <t>0.476±0.073</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.612±0.063</t>
+          <t>0.638±0.015</t>
         </is>
       </c>
     </row>
@@ -3997,216 +3997,162 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MCOS</t>
+          <t>VGO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.1928 ± 0.1729</t>
+          <t>0.1239 ± 0.0288</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.1226 ± 0.1012</t>
+          <t>0.0176 ± 0.0133</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.3436 ± 0.4426</t>
+          <t>0.2587 ± 0.0604</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>45.6293 ± 40.9636</t>
+          <t>28.1101 ± 2.6964</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UGO</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.0759 ± 0.0188</t>
+          <t>0.0892 ± 0.0673</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0053 ± 0.0045</t>
+          <t>0.0289 ± 0.0474</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.1358 ± 0.0357</t>
+          <t>0.1484 ± 0.1114</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17.9600 ± 4.4642</t>
+          <t>19.5066 ± 12.6794</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MLOTST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.0580 ± 0.0878</t>
+          <t>0.0770 ± 0.0789</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0156 ± 0.0219</t>
+          <t>0.0060 ± 0.0264</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.0996 ± 0.1688</t>
+          <t>0.2022 ± 0.1682</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13.7172 ± 20.7582</t>
+          <t>16.5086 ± 15.7372</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MSEN</t>
+          <t>UGO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0531 ± 0.0375</t>
+          <t>0.0591 ± 0.0062</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0468 ± 0.0690</t>
+          <t>0.0057 ± 0.0097</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.0842 ± 0.0876</t>
+          <t>0.1093 ± 0.0055</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12.5638 ± 8.8911</t>
+          <t>13.5221 ± 0.4407</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MLOTST</t>
+          <t>MCOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.0426 ± 0.0257</t>
+          <t>0.0068 ± 0.0022</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0283 ± 0.0223</t>
+          <t>0.0107 ± 0.0013</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.0771 ± 0.0320</t>
+          <t>0.0217 ± 0.0015</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10.0754 ± 6.0885</t>
+          <t>1.5958 ± 0.7276</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VGO</t>
+          <t>MSEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.0335 ± 0.0412</t>
+          <t>-0.0045 ± 0.0111</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0013 ± 0.0034</t>
+          <t>0.0280 ± 0.0644</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.0645 ± 0.0869</t>
+          <t>0.0005 ± 0.0124</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7.9206 ± 9.7360</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TOB</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>0.0187 ± 0.0126</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0.0096 ± 0.0117</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0.0339 ± 0.0266</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>4.4120 ± 2.9653</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>SO</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0.0113 ± 0.0025</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>-0.0156 ± 0.0008</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>0.0237 ± 0.0079</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2.6807 ± 0.5871</t>
+          <t>-1.2242 ± 2.6975</t>
         </is>
       </c>
     </row>

--- a/modelado/modelos/resultados/Regre/DL_reg.xlsx
+++ b/modelado/modelos/resultados/Regre/DL_reg.xlsx
@@ -619,7 +619,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9420225" cy="2847975"/>
+    <ext cx="9315450" cy="2847975"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -3870,7 +3870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:I11"/>
+  <dimension ref="A2:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -3923,47 +3923,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.438±0.060</t>
+          <t>0.423±0.001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.669±0.038</t>
+          <t>0.674±0.012</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.149±0.045</t>
+          <t>0.149±0.019</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.328±0.071</t>
+          <t>1.346±0.001</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.115±0.006</t>
+          <t>0.117±0.000</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.744±0.074</t>
+          <t>0.725±0.003</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.140±0.082</t>
+          <t>-0.204±0.063</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.476±0.073</t>
+          <t>0.519±0.023</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.638±0.015</t>
+          <t>0.585±0.021</t>
         </is>
       </c>
     </row>
@@ -4002,157 +4002,103 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.1239 ± 0.0288</t>
+          <t>0.1456 ± 0.0135</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0176 ± 0.0133</t>
+          <t>0.0098 ± 0.0135</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.2587 ± 0.0604</t>
+          <t>0.2907 ± 0.0209</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28.1101 ± 2.6964</t>
+          <t>34.3694 ± 3.0880</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>UGO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.0892 ± 0.0673</t>
+          <t>0.1406 ± 0.0158</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0289 ± 0.0474</t>
+          <t>-0.0024 ± 0.0065</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.1484 ± 0.1114</t>
+          <t>0.2811 ± 0.0301</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19.5066 ± 12.6794</t>
+          <t>33.2149 ± 3.8318</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MLOTST</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.0770 ± 0.0789</t>
+          <t>0.0524 ± 0.0926</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0060 ± 0.0264</t>
+          <t>0.1101 ± 0.0052</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.2022 ± 0.1682</t>
+          <t>0.0970 ± 0.2193</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16.5086 ± 15.7372</t>
+          <t>12.4007 ± 21.8931</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UGO</t>
+          <t>SPM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0591 ± 0.0062</t>
+          <t>-0.0177 ± 0.0011</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0057 ± 0.0097</t>
+          <t>-0.0157 ± 0.0171</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.1093 ± 0.0055</t>
+          <t>-0.0495 ± 0.0148</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>13.5221 ± 0.4407</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>MCOS</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>0.0068 ± 0.0022</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0.0107 ± 0.0013</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.0217 ± 0.0015</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1.5958 ± 0.7276</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>MSEN</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>-0.0045 ± 0.0111</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0.0280 ± 0.0644</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.0005 ± 0.0124</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>-1.2242 ± 2.6975</t>
+          <t>-4.1865 ± 0.2725</t>
         </is>
       </c>
     </row>
